--- a/Assistants/Info_Duties_Schedule.xlsx
+++ b/Assistants/Info_Duties_Schedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfani/Github/hosseinfani/imitation_game/Assistants/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfani/Google/Academic/UVic/Course/CSC503 Data Mining/2026_Fall_Hossein/Assistants/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CDE0D3-E2ED-444E-8D69-D69B82E27B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F72AFAC-E25E-B643-9031-CB4D0543BC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33520" windowHeight="21580" xr2:uid="{2C32AA88-CB60-44B0-A959-D17D6FFE0192}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33520" windowHeight="21100" activeTab="2" xr2:uid="{2C32AA88-CB60-44B0-A959-D17D6FFE0192}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="4" r:id="rId1"/>
@@ -51,7 +51,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -73,8 +73,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="5">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -84,12 +98,18 @@
     <bk>
       <rc t="1" v="2"/>
     </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="94">
   <si>
     <t>Photo</t>
   </si>
@@ -148,9 +168,6 @@
     <t>Shikha</t>
   </si>
   <si>
-    <t>shikhamallick@uvic.ca</t>
-  </si>
-  <si>
     <t>Shahzad</t>
   </si>
   <si>
@@ -172,9 +189,6 @@
     <t>Ali</t>
   </si>
   <si>
-    <t>alimorty@uvic.ca</t>
-  </si>
-  <si>
     <t>All</t>
   </si>
   <si>
@@ -194,27 +208,6 @@
   </si>
   <si>
     <t>Emergency Marker</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Be Responsive: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Within a second or minute, reply, like, …, to the messages in ms-teams or email.</t>
-    </r>
   </si>
   <si>
     <t>Shikha (w/ Ali) 
@@ -288,12 +281,13 @@
     <t>In case of appeal, refer to the Lab Instructor.</t>
   </si>
   <si>
+    <t>luizpedrofg@gmail.com
+luizguerra@uvic.ca</t>
+  </si>
+  <si>
     <t>Computer Science PhD student on Artificial Inteligence and Software Architecture, graduated on Software Engineering.</t>
   </si>
   <si>
-    <t>to be added to teams</t>
-  </si>
-  <si>
     <t>SUN</t>
   </si>
   <si>
@@ -313,9 +307,6 @@
   </si>
   <si>
     <t>SAT</t>
-  </si>
-  <si>
-    <t>Instructor</t>
   </si>
   <si>
     <t>Marking</t>
@@ -334,16 +325,6 @@
     <t>Release Marks, Stats, and Make Announcement</t>
   </si>
   <si>
-    <t>Lecture A
-2:30-3:30
-David Strong Building C103: Hossein</t>
-  </si>
-  <si>
-    <t>Office A
-3:30-4:30
-ECS611: Hossein</t>
-  </si>
-  <si>
     <t>Markers (Taimoor and Shikha)</t>
   </si>
   <si>
@@ -353,33 +334,14 @@
     <t>Submission Deadline Midnight</t>
   </si>
   <si>
-    <t>Mark Release Deadline Morning</t>
+    <t>taimoor.shahzad659@gmail.com
+tshahzad@uvic.ca</t>
   </si>
   <si>
     <t>I am an MEng student in Electrical and Computer Engineering at the University of Victoria, with a focus on data science and machine learning. I recently completed a one-year co-op as a Data and Business Intelligence Analyst at the BC Energy Regulator, where I worked with SQL, PL/SQL, data modelling, data integration, and analytics. My academic experience includes machine learning, applied data analysis, optimization, NLP, and reinforcement learning. I have also previously served as a Lab TA for ECE 216 and ECE 365.</t>
   </si>
   <si>
     <t>I am a PhD student in the department of Computer Science supervised by Dr. Kevin Stanley. I am currently researching the relationship between how information is observed and modeled through the lens of algorithmic information theory for applications in human mobility modelling. My other research interests include learning theory, game theory, computer vision, and game analytics. My hobbies include esports, game design, card games, cooking, and scuba diving.  I have also worked as a Teaching Assistant for Data Mining for about 2 years and taught SENG 474 in Summer 2026.</t>
-  </si>
-  <si>
-    <t>B02
-10:30 - 11:20
-Engineering Lab Wing B215: Reia</t>
-  </si>
-  <si>
-    <t>B03
-10:30 - 11:20
-Engineering Lab Wing B215: Reia</t>
-  </si>
-  <si>
-    <t>B04
-11:30 - 12:20
-Engineering Lab Wing B215: Ali</t>
-  </si>
-  <si>
-    <t>B05
-13:30 - 14:20
-Engineering Lab Wing B215: Ali</t>
   </si>
   <si>
     <r>
@@ -412,10 +374,92 @@
     <t>Lab Instructor (Ali)</t>
   </si>
   <si>
-    <t>tshahzad@uvic.ca</t>
-  </si>
-  <si>
-    <t>luizguerra@uvic.ca</t>
+    <t>I'm a PhD Candidate at UVic working on Machine Learning Theory, Sequential prediction, Game Theory, and Modern Machine Learning (Deep Learning) Theory.</t>
+  </si>
+  <si>
+    <t>alimorty@uvic.ca
+https://alimorty.github.io/</t>
+  </si>
+  <si>
+    <t>Shikha Mallick is a PhD candidate in the Department of Computer Science at the University of Victoria, BC, Canada. Her research lies at the intersection of LLMs, reinforcement learning, graph mining, fairness, and computational social science. Her current work focuses on mitigating bias in social networks and on designing evaluation frameworks for structurally realistic and socially responsible synthetic networks.</t>
+  </si>
+  <si>
+    <t>shikhamallick@uvic.ca
+https://mshik.github.io/</t>
+  </si>
+  <si>
+    <t>ECS 654</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Please Be Responsive: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Within a second or minute, reply, like, …, to the messages in ms-teams or email.</t>
+    </r>
+  </si>
+  <si>
+    <t>Instructor (Hossein)</t>
+  </si>
+  <si>
+    <t>Students</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Submission Manual
+Prev. Submission Marks Release </t>
+  </si>
+  <si>
+    <t>B02: 10:30 - 11:20
+Engineering Lab Wing B215: Reia</t>
+  </si>
+  <si>
+    <t>B03: 10:30 - 11:20
+Engineering Lab Wing B215: Reia</t>
+  </si>
+  <si>
+    <t>B04: 11:30 - 12:20
+Engineering Lab Wing B215: Ali</t>
+  </si>
+  <si>
+    <t>B05: 13:30 - 14:20
+Engineering Lab Wing B215: Ali</t>
+  </si>
+  <si>
+    <t>Lecture A: 2:30-3:30
+Strong Building C103: Hossein</t>
+  </si>
+  <si>
+    <t>Office A: 3:30-4:30
+ECS613: Hossein</t>
+  </si>
+  <si>
+    <t>Office C: 3:30-4:30
+ECS613: Hossein</t>
+  </si>
+  <si>
+    <t>Office B: 3:30-4:30
+ECS613: Hossein</t>
+  </si>
+  <si>
+    <t>Lecture B: 2:30-3:30
+Strong Building C103: Hossein</t>
+  </si>
+  <si>
+    <t>Lecture C: 2:30-3:30
+Strong Building C103: Hossein</t>
   </si>
 </sst>
 </file>
@@ -510,7 +554,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -565,8 +609,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -766,25 +816,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -908,6 +945,9 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -920,9 +960,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -968,11 +1005,20 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1156,7 +1202,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1167,6 +1213,14 @@
   </rv>
   <rv s="0">
     <v>2</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -1186,6 +1240,8 @@
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
 </richValueRels>
 </file>
 
@@ -1495,7 +1551,7 @@
     <col min="4" max="4" width="13" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.5" style="49" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" style="50" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="83" style="2" customWidth="1"/>
     <col min="9" max="16384" width="18.1640625" style="2"/>
   </cols>
@@ -1504,10 +1560,10 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="69"/>
+      <c r="C1" s="72"/>
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
@@ -1517,7 +1573,7 @@
       <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="48" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="5" t="s">
@@ -1531,85 +1587,95 @@
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>23</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="49">
+        <v>70</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="127" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="48">
+      <c r="C3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="49">
         <v>70</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H3" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="49">
+        <v>50</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="127" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8"/>
-      <c r="B3" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="48">
+    <row r="5" spans="1:10" ht="152" x14ac:dyDescent="0.2">
+      <c r="A5" s="51" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="49">
+        <v>50</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:10" ht="121.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="51" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="48">
-        <v>50</v>
-      </c>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5" spans="1:10" ht="152" x14ac:dyDescent="0.2">
-      <c r="A5" s="50" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="48">
-        <v>50</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="6" spans="1:10" ht="156" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="e" vm="3">
+      <c r="A6" s="11" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -1619,15 +1685,15 @@
         <v>16</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="9" t="s">
-        <v>86</v>
+      <c r="E6" s="47" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="48">
+      <c r="G6" s="49">
         <v>30</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -1646,15 +1712,14 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" tooltip="mailto:shikhamallick@uvic.ca" display="mailto:shikhamallick@uvic.ca" xr:uid="{88877183-5890-B246-978E-B20A9162922B}"/>
-    <hyperlink ref="E5" r:id="rId2" xr:uid="{E3A6076F-235D-4445-BA78-D68715E854CE}"/>
-    <hyperlink ref="E2" r:id="rId3" tooltip="mailto:reiadrucker@uvic.ca" display="mailto:reiadrucker@uvic.ca" xr:uid="{727DFD4E-54B3-874F-92E8-82A8A8238178}"/>
-    <hyperlink ref="E3" r:id="rId4" tooltip="mailto:alimorty@uvic.ca" display="mailto:alimorty@uvic.ca" xr:uid="{C0466608-A3F8-1745-AE4A-E1B5E92D4169}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{CF1008B3-1577-3E48-8902-4ECF3CEEB153}"/>
+    <hyperlink ref="E5" r:id="rId1" tooltip="mailto:taimoor.shahzad659@gmail.com" display="mailto:taimoor.shahzad659@gmail.com" xr:uid="{E3A6076F-235D-4445-BA78-D68715E854CE}"/>
+    <hyperlink ref="E2" r:id="rId2" tooltip="mailto:reiadrucker@uvic.ca" display="mailto:reiadrucker@uvic.ca" xr:uid="{727DFD4E-54B3-874F-92E8-82A8A8238178}"/>
+    <hyperlink ref="E3" r:id="rId3" tooltip="mailto:alimorty@uvic.ca" display="mailto:alimorty@uvic.ca" xr:uid="{C0466608-A3F8-1745-AE4A-E1B5E92D4169}"/>
+    <hyperlink ref="E6" r:id="rId4" tooltip="mailto:luizpedrofg@gmail.com" display="mailto:luizpedrofg@gmail.com" xr:uid="{CF1008B3-1577-3E48-8902-4ECF3CEEB153}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -1685,29 +1750,29 @@
         <v>11</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="19"/>
       <c r="C3" s="20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="19"/>
       <c r="C4" s="20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="21"/>
       <c r="B5" s="22"/>
       <c r="C5" s="23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.2">
@@ -1718,7 +1783,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="26"/>
     </row>
@@ -1732,7 +1797,7 @@
       <c r="A9" s="27"/>
       <c r="B9" s="28"/>
       <c r="C9" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="26"/>
     </row>
@@ -1746,7 +1811,7 @@
       <c r="A11" s="27"/>
       <c r="B11" s="28"/>
       <c r="C11" s="20" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D11" s="26"/>
     </row>
@@ -1760,7 +1825,7 @@
       <c r="A13" s="29"/>
       <c r="B13" s="30"/>
       <c r="C13" s="31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="26"/>
     </row>
@@ -1771,13 +1836,13 @@
     </row>
     <row r="15" spans="1:4" ht="38" x14ac:dyDescent="0.2">
       <c r="A15" s="43" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B15" s="33" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1789,21 +1854,21 @@
       <c r="A17" s="34"/>
       <c r="B17" s="35"/>
       <c r="C17" s="20" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="57" x14ac:dyDescent="0.2">
       <c r="A18" s="34"/>
       <c r="B18" s="35"/>
       <c r="C18" s="20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="34"/>
       <c r="B19" s="35"/>
       <c r="C19" s="20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -1815,7 +1880,7 @@
       <c r="A21" s="34"/>
       <c r="B21" s="35"/>
       <c r="C21" s="20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -1827,7 +1892,7 @@
       <c r="A23" s="34"/>
       <c r="B23" s="35"/>
       <c r="C23" s="20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -1839,7 +1904,7 @@
       <c r="A25" s="36"/>
       <c r="B25" s="37"/>
       <c r="C25" s="23" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -1848,13 +1913,13 @@
     </row>
     <row r="27" spans="1:3" ht="38" x14ac:dyDescent="0.2">
       <c r="A27" s="44" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B27" s="38" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -1866,7 +1931,7 @@
       <c r="A29" s="39"/>
       <c r="B29" s="40"/>
       <c r="C29" s="20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -1878,7 +1943,7 @@
       <c r="A31" s="39"/>
       <c r="B31" s="40"/>
       <c r="C31" s="20" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -1890,14 +1955,14 @@
       <c r="A33" s="39"/>
       <c r="B33" s="40"/>
       <c r="C33" s="20" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="38" x14ac:dyDescent="0.2">
       <c r="A34" s="39"/>
       <c r="B34" s="40"/>
       <c r="C34" s="20" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -1909,35 +1974,35 @@
       <c r="A36" s="39"/>
       <c r="B36" s="40"/>
       <c r="C36" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A37" s="39"/>
       <c r="B37" s="40"/>
       <c r="C37" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A38" s="39"/>
       <c r="B38" s="40"/>
       <c r="C38" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A39" s="39"/>
       <c r="B39" s="40"/>
       <c r="C39" s="20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="19" x14ac:dyDescent="0.2">
       <c r="A40" s="41"/>
       <c r="B40" s="42"/>
       <c r="C40" s="23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1951,13 +2016,13 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="20.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" style="59" customWidth="1"/>
-    <col min="2" max="2" width="31.1640625" style="52" customWidth="1"/>
+    <col min="1" max="1" width="29.1640625" style="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.83203125" style="52" customWidth="1"/>
     <col min="3" max="3" width="34.83203125" style="52" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" style="52" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="52" customWidth="1"/>
-    <col min="6" max="6" width="24" style="52" customWidth="1"/>
-    <col min="7" max="7" width="5.1640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.83203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.33203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="52" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.5" style="52" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="45.6640625" style="52" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="20.1640625" style="52"/>
@@ -1966,150 +2031,152 @@
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="52"/>
       <c r="B1" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="F1" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="G1" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="60" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="61" t="s">
-        <v>63</v>
-      </c>
       <c r="H1" s="62" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I1" s="61" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52"/>
-      <c r="B2" s="65" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="A2" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="63" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>78</v>
+        <v>73</v>
+      </c>
+      <c r="C3" s="54" t="s">
+        <v>84</v>
       </c>
       <c r="D3" s="54" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F3" s="53"/>
       <c r="G3" s="53"/>
     </row>
-    <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>80</v>
+    <row r="4" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="68" t="s">
+        <v>86</v>
       </c>
       <c r="F4" s="53"/>
       <c r="G4" s="53"/>
     </row>
-    <row r="5" spans="1:9" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="63" t="s">
-        <v>84</v>
+    <row r="5" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="69" t="s">
+        <v>74</v>
       </c>
       <c r="B5" s="53"/>
       <c r="C5" s="55"/>
-      <c r="D5" s="54" t="s">
-        <v>81</v>
+      <c r="D5" s="68" t="s">
+        <v>87</v>
       </c>
       <c r="E5" s="53"/>
       <c r="F5" s="53"/>
       <c r="G5" s="53"/>
     </row>
-    <row r="6" spans="1:9" ht="68" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="64" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E6" s="56" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
     </row>
-    <row r="7" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A7" s="64" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E7" s="56" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
     </row>
     <row r="8" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" s="65" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B8" s="53"/>
       <c r="C8" s="53"/>
-      <c r="D8" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
+      <c r="D8" s="73" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
       <c r="G8" s="53"/>
       <c r="I8" s="66" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="71" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
+      <c r="A9" s="74" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
       <c r="G9" s="53"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="72"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="57" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E10" s="57" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G10" s="53"/>
       <c r="I10" s="58" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2124,6 +2191,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100629F52BD7A8CB0489035B85AC7EDFBA2" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d70325b7b4dea4f962e45496877bebf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="93a39aae-0c10-44f4-bcca-ab93ec7b7056" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="21eb934b69573e8a55735126159b9760" ns2:_="">
     <xsd:import namespace="93a39aae-0c10-44f4-bcca-ab93ec7b7056"/>
@@ -2255,22 +2337,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51F09107-E06C-4F36-AF05-7455D6286771}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6613811F-E7F2-4F0C-86B9-5CC1965DCE0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4538749-1078-48DE-9DC6-5CA94318747E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2286,21 +2370,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51F09107-E06C-4F36-AF05-7455D6286771}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6613811F-E7F2-4F0C-86B9-5CC1965DCE0D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>